--- a/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
+++ b/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Rathbones Investment Management Limited — Cash Flow Summary by Year</a:t>
+              <a:t>Rathbones Investment Management Limited — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -295,6 +300,30 @@
           <val>
             <numRef>
               <f>'Overview'!$J$8:$N$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!I9</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$J$5:$N$5</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$J$9:$N$9</f>
             </numRef>
           </val>
         </ser>
@@ -326,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -366,13 +395,535 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Rathbones Investment Management Limited — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t xml:space="preserve"> (£'000)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Rathbones Investment Management Limited — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t xml:space="preserve"> (£'000)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Rathbones Investment Management Limited — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG25</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$24:$AL$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t xml:space="preserve"> (£'000)</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -404,30 +955,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -459,8 +1010,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -499,12 +1050,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>14</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -514,9 +1065,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -526,19 +1077,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>36</row>
+      <row>55</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>77</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>99</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>121</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -836,7 +1453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V12"/>
+  <dimension ref="A1:AT31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -859,6 +1476,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -871,14 +1512,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary ( (£'000))</t>
+          <t>Balance Sheet Summary ( (£'000))</t>
         </is>
       </c>
     </row>
@@ -938,27 +1579,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -967,45 +1608,45 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash inflow/(outflow) from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>988180</v>
+        <v>4809683</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>200256</v>
+        <v>3017731</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>-99468</v>
+        <v>2845759</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>276728</v>
+        <v>3081068</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>-249109</v>
+        <v>2843239</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash inflow/(outflow) from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>-249109</v>
+        <v>2843239</v>
       </c>
       <c r="K6" t="n">
-        <v>276728</v>
+        <v>3081068</v>
       </c>
       <c r="L6" t="n">
-        <v>-99468</v>
+        <v>2845759</v>
       </c>
       <c r="M6" t="n">
-        <v>200256</v>
+        <v>3017731</v>
       </c>
       <c r="N6" t="n">
-        <v>988180</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>4809683</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
@@ -1014,137 +1655,749 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>-559268</v>
+        <v>206392</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-2375</v>
+        <v>124556</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-256406</v>
+        <v>131817</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-285059</v>
+        <v>205120</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>-126903</v>
+        <v>194424</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Loans and advances to customers</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>-126903</v>
+        <v>194424</v>
       </c>
       <c r="K7" t="n">
-        <v>-285059</v>
+        <v>205120</v>
       </c>
       <c r="L7" t="n">
-        <v>-256406</v>
+        <v>131817</v>
       </c>
       <c r="M7" t="n">
-        <v>-2375</v>
+        <v>124556</v>
       </c>
       <c r="N7" t="n">
-        <v>-559268</v>
+        <v>206392</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Due to customers</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>3474635</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>2540560</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>2359342</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>2622664</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>2390232</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Due to customers</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>2390232</v>
+      </c>
+      <c r="K8" t="n">
+        <v>2622664</v>
+      </c>
+      <c r="L8" t="n">
+        <v>2359342</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2540560</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3474635</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>1147348</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>405212</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>415845</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>415887</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>409920</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>409920</v>
+      </c>
+      <c r="K9" t="n">
+        <v>415887</v>
+      </c>
+      <c r="L9" t="n">
+        <v>415845</v>
+      </c>
+      <c r="M9" t="n">
+        <v>405212</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1147348</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Profit &amp; Loss Summary ( (£'000))</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>781638</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>424964</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>385751</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>351147</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>352939</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>352939</v>
+      </c>
+      <c r="S13" t="n">
+        <v>351147</v>
+      </c>
+      <c r="T13" t="n">
+        <v>385751</v>
+      </c>
+      <c r="U13" t="n">
+        <v>424964</v>
+      </c>
+      <c r="V13" t="n">
+        <v>781638</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-670165</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-403797</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-321887</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-301973</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-277741</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-277741</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-301973</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-321887</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-403797</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-670165</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>81117</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>16367</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>49958</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>40967</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>58964</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit for the year</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>58964</v>
+      </c>
+      <c r="S15" t="n">
+        <v>40967</v>
+      </c>
+      <c r="T15" t="n">
+        <v>49958</v>
+      </c>
+      <c r="U15" t="n">
+        <v>16367</v>
+      </c>
+      <c r="V15" t="n">
+        <v>81117</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary ( (£'000))</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>405212</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>415845</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>415887</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>409920</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>405956</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>405956</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>409920</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>415887</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>415845</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>405212</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>81117</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>16367</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>49958</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>40967</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>58964</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>58964</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>40967</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>49958</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>16367</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>81117</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>1147348</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>405212</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>415845</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>415887</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>409920</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>409920</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>415887</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>415845</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>405212</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1147348</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary ( (£'000))</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL24" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Net cash inflow/(outflow) from operating activities</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>988180</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>200256</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>-99468</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>276728</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-249109</v>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>Net cash inflow/(outflow) from operating activities</t>
+        </is>
+      </c>
+      <c r="AH25" t="n">
+        <v>-249109</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>276728</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>-99468</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>200256</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>988180</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>-559268</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>-2375</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-256406</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>-285059</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-126903</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>-126903</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>-285059</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>-256406</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>-2375</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>-559268</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
           <t>Cash and cash equivalents at the end of the year</t>
         </is>
       </c>
-      <c r="B8" s="5" t="n">
+      <c r="B27" s="5" t="n">
         <v>1609394</v>
       </c>
-      <c r="C8" s="5" t="n">
+      <c r="C27" s="5" t="n">
         <v>1249482</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D27" s="5" t="n">
         <v>1078601</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E27" s="5" t="n">
         <v>1484475</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F27" s="5" t="n">
         <v>1530445</v>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="AG27" t="inlineStr">
         <is>
           <t>Cash and cash equivalents at the end of the year</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="AH27" t="n">
         <v>1530445</v>
       </c>
-      <c r="K8" t="n">
+      <c r="AI27" t="n">
         <v>1484475</v>
       </c>
-      <c r="L8" t="n">
+      <c r="AJ27" t="n">
         <v>1078601</v>
       </c>
-      <c r="M8" t="n">
+      <c r="AK27" t="n">
         <v>1249482</v>
       </c>
-      <c r="N8" t="n">
+      <c r="AL27" t="n">
         <v>1609394</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>Pillar 3 Key Metrics</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>Line item</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D30" s="4" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
+      <c r="E30" s="4" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="F30" s="4" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1172,7 +2425,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Leverage Ratio</t>
+          <t>Rathbones Investment Management Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
@@ -1214,7 +2467,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Leverage Ratio</t>
+          <t>Tier 1 Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1293,7 +2546,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — LCR</t>
+          <t>Rathbones Investment Management Limited — Total Capital</t>
         </is>
       </c>
     </row>
@@ -1335,7 +2588,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>LCR</t>
+          <t>Total Capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1414,7 +2667,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — NSFR</t>
+          <t>Rathbones Investment Management Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
@@ -1456,7 +2709,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>NSFR</t>
+          <t>Total Capital Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1535,6 +2788,607 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Rathbones Investment Management Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed at entity level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>RWA Breakdown</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="180" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — Leverage Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Leverage Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — LCR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>LCR</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — NSFR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>NSFR</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
           <t>Rathbones Investment Management Limited — MREL Ratio</t>
         </is>
       </c>
@@ -1637,6 +3491,1650 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Entity basis, £'000. Blank cells indicate a line not disclosed that year (0 indicates a line disclosed as nil, not a gap).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances with central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>1503963</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>1165956</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1038280</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1412915</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>1463293</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Settlement balances</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>44654</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>35248</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>39048</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>19825</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>28831</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to banks</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>105394</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>83482</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>42601</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>106475</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>97887</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>206392</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>124556</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>131817</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>205120</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>194424</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Investment securities - fair value through profit and loss</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n">
+        <v>1181</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>3146</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>2558</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Investment securities - amortised cost</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>1864282</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>1278219</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>1294589</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>1045234</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>761654</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Prepayments, accrued income and other assets</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>209933</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>147396</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>118622</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>92179</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>85601</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>48050</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>10939</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>7783</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>12341</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>12496</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Right of use assets</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Current tax asset</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>6770</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>7992</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>2130</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>3520</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>2826</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax asset</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n">
+        <v>1116</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1158</v>
+      </c>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Intangible assets</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>779332</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>153029</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>158751</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>170498</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>183788</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Investments in subsidiary undertakings</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>40913</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>9798</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>9798</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>9798</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>9798</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="n">
+        <v>4809683</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3017731</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2845759</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3081068</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>2843239</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Deposits by banks</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>8410</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>3770</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>12359</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>1035</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2213</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Settlement balances</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>63146</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>47225</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>41942</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>31028</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>27118</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Due to customers</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>3474635</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>2540560</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>2359342</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>2622664</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>2390232</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Accruals, deferred income, provisions and other liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>41844</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>20964</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>16271</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>8736</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>9432</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Lease liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax liability</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>74300</v>
+      </c>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n">
+        <v>1718</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>4243</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>3662335</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>2612519</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>2429914</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>2665181</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>2433319</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n">
+        <v>4996</v>
+      </c>
+      <c r="C28" s="6" t="n">
+        <v>4996</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>4996</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>4996</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>4996</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Share premium</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>751899</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>298066</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>298066</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>298066</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>298066</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-21897</v>
+      </c>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>412350</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>102150</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>112783</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>112825</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>106858</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>1147348</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>405212</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>415845</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>415887</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>409920</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>4809683</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>3017731</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>2845759</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>3081068</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>2843239</v>
+      </c>
+    </row>
+    <row r="35" ht="280" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory accounts, entity basis, GBP'000.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, Statement of comprehensive income p.22, Statement of changes in equity p.23, Balance sheet p.24 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.25/26/27 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.26/27/28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.26/27/29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A35:F35"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F27"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="76" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — Profit &amp; Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Entity basis, £'000. Statement of comprehensive income; all comprehensive income each year is attributable to equity holders of the Company.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£'000)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£'000)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£'000)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£'000)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£'000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest and similar income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>155597</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>137333</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>123040</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>43908</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>7577</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest expense and similar charges</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-72439</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-80881</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-73395</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-21293</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-193</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>83158</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>56452</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>49645</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>22615</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7384</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>626296</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>352499</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>318826</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>318304</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>335389</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission expense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-3515</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-3050</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-2811</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-3666</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-4016</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee and commission income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>622781</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>349449</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>316015</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>314638</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>331373</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Intra-group management charges</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>16754</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>13433</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>13760</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>12705</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>13518</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Dividends from subsidiaries</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>57002</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Other operating income</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>1943</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>630</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>1331</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>781638</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>424964</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>385751</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>351147</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>352939</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Charges in relation to client relationships and goodwill</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>-32717</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>-13244</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>-12593</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-13311</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-13515</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Impairment in investment in subsidiaries</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-43888</v>
+      </c>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Other operating expenses</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-593560</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-390553</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-309294</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-288662</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-264226</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>-670165</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>-403797</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-321887</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-301973</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-277741</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>111473</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>21167</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>63864</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>49174</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>75198</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Taxation</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>-30356</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>-4800</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>-13906</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-8207</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>-16234</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Profit for the year attributable to equity holders of the Company</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>81117</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>16367</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>49958</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>40967</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>58964</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Other comprehensive income for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>81117</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>16367</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>49958</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>40967</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>58964</v>
+      </c>
+    </row>
+    <row r="27" ht="280" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory accounts, entity basis, GBP'000.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, Statement of comprehensive income p.22, Statement of changes in equity p.23, Balance sheet p.24 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.25/26/27 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.26/27/28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.26/27/29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A27:F27"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Chronological roll-forward, oldest to newest, entity basis, £'000. Equity reconciliation ladder confirmed: every year's own closing balance ties exactly to both the next year's own opening balance and that year's own Balance Sheet Total equity - zero undocumented plug rows across all 5 years, including FY2025's four separate movements (business transfer, share issue, share premium cancellation, other).</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Share premium</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>At 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>4996</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>298066</v>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n">
+        <v>102894</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>405956</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2021)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n"/>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n">
+        <v>58964</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>58964</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid (FY2021)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n"/>
+      <c r="E6" s="6" t="n">
+        <v>-55000</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-55000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>4996</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>298066</v>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n">
+        <v>106858</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>409920</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2022)</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n"/>
+      <c r="C8" s="5" t="n"/>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n">
+        <v>40967</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>40967</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid (FY2022)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n">
+        <v>-35000</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-35000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>4996</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>298066</v>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n">
+        <v>112825</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>415887</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2023)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n"/>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n">
+        <v>49958</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>49958</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid (FY2023)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n">
+        <v>-50000</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-50000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>4996</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>298066</v>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n">
+        <v>112783</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>415845</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2024)</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n"/>
+      <c r="C14" s="5" t="n"/>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n">
+        <v>16367</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>16367</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid (FY2024)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n">
+        <v>-27000</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-27000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="n">
+        <v>4996</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>298066</v>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n">
+        <v>102150</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>405212</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year (FY2025)</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n">
+        <v>81117</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>81117</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Dividends paid (FY2025)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n">
+        <v>-69000</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-69000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Arisen from business transfer (FY2025)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n">
+        <v>-21897</v>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n">
+        <v>-21897</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Issue of share capital (FY2025)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n">
+        <v>751898</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n">
+        <v>751898</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Cancellation of share premium (FY2025)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n">
+        <v>-298065</v>
+      </c>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n">
+        <v>298065</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Other movement (FY2025)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>At 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="n">
+        <v>4996</v>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>751899</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-21897</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>412350</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>1147348</v>
+      </c>
+    </row>
+    <row r="25" ht="260" customHeight="1">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory accounts, entity basis, GBP'000.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, Statement of comprehensive income p.22, Statement of changes in equity p.23, Balance sheet p.24 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.25/26/27 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.26/27/28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.26/27/29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2417,16 +5915,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="90" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2437,465 +5935,298 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — CET1 Capital</t>
+          <t>Rathbones Investment Management Limited — Asset Quality</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Entity basis, £'000. Loans and advances to customers by product (Note 14); no IFRS 9 Stage 1/2/3 split is disclosed for this book - loans are fully secured against clients' investment portfolios held in Rathbones' nominee name, and the Company's own risk-management note (27) reports £nil-to-negligible impairment losses arising from the loan book in every year covered. (The Company's separate treasury book - money-market/interbank placements, not customer lending - does carry a 12-month/lifetime ECL stage split in note 27, but that reflects counterparty credit risk on Company cash, not loan asset quality, so it is not reproduced here.)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£'000)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£'000)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£'000)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£'000)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£'000)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CET1 Capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
-FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loans and advances to customers, by product</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Overdrafts</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>17710</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>15606</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>9558</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>6238</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>6742</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Loan book</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>146810</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>75942</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>101666</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>159694</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>167981</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Amounts owed by group undertakings</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>39880</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>31935</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>19629</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>38576</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>18936</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Financial planning debtors</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>747</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>718</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>656</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>520</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Other debtors</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>1246</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>417</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>308</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Total before impairment loss allowance</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>206393</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>124618</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>131817</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>205132</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>194424</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Less: impairment loss allowance</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>-62</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Net loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>206392</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>124556</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>131817</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>205120</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>194424</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Asset quality ratio (derived)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Impairment loss allowance as % of gross loans and advances to customers</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>0.05%</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>0.01%</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="280" customHeight="1">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory accounts, entity basis, GBP'000.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, Statement of comprehensive income p.22, Statement of changes in equity p.23, Balance sheet p.24 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.25/26/27 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.26/27/28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.26/27/29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
+Note 14 (Loans and advances to customers) page references - FY2025/FY2024: p.39; FY2024/FY2023: p.41; FY2023/FY2022: p.41 (AR2023); FY2022/FY2021: p.43 (AR2022). FY2025's component lines sum to £206,393k against a reported net total of £206,392k - a genuine £1k source rounding artifact, not a transcription error; the reported net total is used for the Balance Sheet tie-out.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rathbones Investment Management Limited — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CET1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
-FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
-Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rathbones Investment Management Limited — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
-FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
-Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rathbones Investment Management Limited — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
-FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
-Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2921,7 +6252,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Total Capital</t>
+          <t>Rathbones Investment Management Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -2963,7 +6294,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total Capital</t>
+          <t>CET1 Capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3042,7 +6373,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Total Capital Ratio</t>
+          <t>Rathbones Investment Management Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -3084,7 +6415,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total Capital Ratio</t>
+          <t>CET1 Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3163,7 +6494,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Total RWAs</t>
+          <t>Rathbones Investment Management Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -3205,7 +6536,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total RWAs</t>
+          <t>Tier 1 Capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">

--- a/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
+++ b/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
@@ -2535,7 +2535,7 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2551,7 +2551,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2588,43 +2592,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total Capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
+          <t>Regulatory capital resources (own funds) — Company entity level</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>467062</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>261190</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>267182</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>256378</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>237897</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
+          <t>Note: ENTITY-LEVEL own-funds total taken from the Company's own statutory accounts, not from a Pillar 3 template - Rathbones Group Plc's Pillar 3 is consolidated only and discloses nothing at this entity's level. No tier split or RWA accompanies it, so no ratio on this sheet or the Total Capital Ratio / Total RWAs sheets is derivable from it. The FY2024-to-FY2025 near-doubling is genuine and reflects the migration of Investec Wealth &amp; Investment clients into this entity, which also drives the Balance Sheet and equity jump visible on the Overview sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="300" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2634,7 +2628,14 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
+ENTITY-LEVEL REGULATORY CAPITAL RESOURCES (added 2026-09-15). Each year's own Annual Report and Financial Statements, capital-management note (scanned filings - figures read by OCR at 300-400 dpi and confirmed visually):
+FY2025 and FY2024 comparative: 'At 31 December 2025, the Company's regulatory capital resources, including retained earnings for 2025, were GBP467,062,000 (2024: GBP261,190,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 own-year, and FY2023 comparative: 'At 31 December 2024 ... were GBP261,190,000 (2023: GBP267,182,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 own-year, and FY2022 comparative: 'At 31 December 2023 ... were GBP267,182,000 (2022: GBP256,378,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021 own-year: 'At 31 December 2021 ... were GBP237,897,000 (2020: GBP247,786,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+VALIDATION: every year except FY2022 and FY2025 appears in two separate filings and agrees in both - FY2024 reads GBP261,190,000 in both the FY2025 comparative and the FY2024 own-year note, and FY2023 reads GBP267,182,000 in both the FY2024 comparative and the FY2023 own-year note.
+BASIS: this is the Company's total regulatory capital RESOURCES (own funds) as defined in its own note - 'accounting capital and certain deductions from accounting capital, the latter largely in respect of intangible assets', measured against Pillar I and Pillar II requirements under the PRA's application of CRD. The note gives NO tier split and NO risk-weighted assets, so CET1 Capital, Tier 1 Capital, all three capital ratios and Total RWAs remain blank rather than derived - in particular this figure has NOT been copied into CET1 or Tier 1, because the Company nowhere states that its capital is wholly CET1.</t>
         </is>
       </c>
     </row>

--- a/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
+++ b/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
@@ -2503,7 +2503,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2513,7 +2513,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -2618,7 +2622,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="300" customHeight="1">
+    <row r="7" ht="470" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2628,7 +2632,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
 ENTITY-LEVEL REGULATORY CAPITAL RESOURCES (added 2026-09-15). Each year's own Annual Report and Financial Statements, capital-management note (scanned filings - figures read by OCR at 300-400 dpi and confirmed visually):
 FY2025 and FY2024 comparative: 'At 31 December 2025, the Company's regulatory capital resources, including retained earnings for 2025, were GBP467,062,000 (2024: GBP261,190,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2024 own-year, and FY2023 comparative: 'At 31 December 2024 ... were GBP261,190,000 (2023: GBP267,182,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
@@ -2746,7 +2754,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2756,7 +2764,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2879,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2877,7 +2889,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3001,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="180" customHeight="1">
+    <row r="6" ht="430" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2995,7 +3011,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3125,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3115,7 +3135,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3250,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3236,7 +3260,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3375,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3357,7 +3385,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -3468,7 +3500,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3478,7 +3510,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4197,11 @@
 FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.26/27/28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.26/27/29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -4691,7 +4731,11 @@
 FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.26/27/28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.26/27/29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5167,11 @@
 FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.26/27/28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.26/27/29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -5894,7 +5942,7 @@
         <v>1530445</v>
       </c>
     </row>
-    <row r="40" ht="330" customHeight="1">
+    <row r="40" ht="470" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -5904,7 +5952,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -6220,7 +6272,11 @@
 FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.26/27/28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.26/27/29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
 Note 14 (Loans and advances to customers) page references - FY2025/FY2024: p.39; FY2024/FY2023: p.41; FY2023/FY2022: p.41 (AR2023); FY2022/FY2021: p.43 (AR2022). FY2025's component lines sum to £206,393k against a reported net total of £206,392k - a genuine £1k source rounding artifact, not a transcription error; the reported net total is used for the Balance Sheet tie-out.</t>
         </is>
       </c>
@@ -6331,7 +6387,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -6341,7 +6397,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6512,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -6462,7 +6522,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -6573,7 +6637,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="150" customHeight="1">
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -6583,7 +6647,11 @@
 FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
 FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts. The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>

--- a/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
+++ b/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2425,7 +2426,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Tier 1 Ratio</t>
+          <t>Rathbones Investment Management Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2468,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 Ratio</t>
+          <t>Tier 1 Capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2516,6 +2517,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -2539,7 +2541,7 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2550,16 +2552,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Total Capital</t>
+          <t>Rathbones Investment Management Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2596,33 +2594,43 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Regulatory capital resources (own funds) — Company entity level</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>467062</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>261190</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>267182</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>256378</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>237897</v>
+          <t>Tier 1 Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: ENTITY-LEVEL own-funds total taken from the Company's own statutory accounts, not from a Pillar 3 template - Rathbones Group Plc's Pillar 3 is consolidated only and discloses nothing at this entity's level. No tier split or RWA accompanies it, so no ratio on this sheet or the Total Capital Ratio / Total RWAs sheets is derivable from it. The FY2024-to-FY2025 near-doubling is genuine and reflects the migration of Investec Wealth &amp; Investment clients into this entity, which also drives the Balance Sheet and equity jump visible on the Overview sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="470" customHeight="1">
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="430" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2635,15 +2643,9 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
-ENTITY-LEVEL REGULATORY CAPITAL RESOURCES (added 2026-09-15). Each year's own Annual Report and Financial Statements, capital-management note (scanned filings - figures read by OCR at 300-400 dpi and confirmed visually):
-FY2025 and FY2024 comparative: 'At 31 December 2025, the Company's regulatory capital resources, including retained earnings for 2025, were GBP467,062,000 (2024: GBP261,190,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 own-year, and FY2023 comparative: 'At 31 December 2024 ... were GBP261,190,000 (2023: GBP267,182,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 own-year, and FY2022 comparative: 'At 31 December 2023 ... were GBP267,182,000 (2022: GBP256,378,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021 own-year: 'At 31 December 2021 ... were GBP237,897,000 (2020: GBP247,786,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
-VALIDATION: every year except FY2022 and FY2025 appears in two separate filings and agrees in both - FY2024 reads GBP261,190,000 in both the FY2025 comparative and the FY2024 own-year note, and FY2023 reads GBP267,182,000 in both the FY2024 comparative and the FY2023 own-year note.
-BASIS: this is the Company's total regulatory capital RESOURCES (own funds) as defined in its own note - 'accounting capital and certain deductions from accounting capital, the latter largely in respect of intangible assets', measured against Pillar I and Pillar II requirements under the PRA's application of CRD. The note gives NO tier split and NO risk-weighted assets, so CET1 Capital, Tier 1 Capital, all three capital ratios and Total RWAs remain blank rather than derived - in particular this figure has NOT been copied into CET1 or Tier 1, because the Company nowhere states that its capital is wholly CET1.</t>
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2667,7 @@
   <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2676,12 +2678,16 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Total Capital Ratio</t>
+          <t>Rathbones Investment Management Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2718,43 +2724,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total Capital Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
+          <t>Regulatory capital resources (own funds) — Company entity level</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>467062</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>261190</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>267182</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>256378</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>237897</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="430" customHeight="1">
+          <t>Note: ENTITY-LEVEL own-funds total taken from the Company's own statutory accounts, not from a Pillar 3 template - Rathbones Group Plc's Pillar 3 is consolidated only and discloses nothing at this entity's level. No tier split or RWA accompanies it, so no ratio on this sheet or the Total Capital Ratio / Total RWAs sheets is derivable from it. The FY2024-to-FY2025 near-doubling is genuine and reflects the migration of Investec Wealth &amp; Investment clients into this entity, which also drives the Balance Sheet and equity jump visible on the Overview sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="470" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2767,8 +2763,16 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
+ENTITY-LEVEL REGULATORY CAPITAL RESOURCES (added 2026-09-15). Each year's own Annual Report and Financial Statements, capital-management note (scanned filings - figures read by OCR at 300-400 dpi and confirmed visually):
+FY2025 and FY2024 comparative: 'At 31 December 2025, the Company's regulatory capital resources, including retained earnings for 2025, were GBP467,062,000 (2024: GBP261,190,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 own-year, and FY2023 comparative: 'At 31 December 2024 ... were GBP261,190,000 (2023: GBP267,182,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 own-year, and FY2022 comparative: 'At 31 December 2023 ... were GBP267,182,000 (2022: GBP256,378,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021 own-year: 'At 31 December 2021 ... were GBP237,897,000 (2020: GBP247,786,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+VALIDATION: every year except FY2022 and FY2025 appears in two separate filings and agrees in both - FY2024 reads GBP261,190,000 in both the FY2025 comparative and the FY2024 own-year note, and FY2023 reads GBP267,182,000 in both the FY2024 comparative and the FY2023 own-year note.
+BASIS: this is the Company's total regulatory capital RESOURCES (own funds) as defined in its own note - 'accounting capital and certain deductions from accounting capital, the latter largely in respect of intangible assets', measured against Pillar I and Pillar II requirements under the PRA's application of CRD. The note gives NO tier split and NO risk-weighted assets, so CET1 Capital, Tier 1 Capital, all three capital ratios and Total RWAs remain blank rather than derived - in particular this figure has NOT been copied into CET1 or Tier 1, because the Company nowhere states that its capital is wholly CET1.</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2805,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Total RWAs</t>
+          <t>Rathbones Investment Management Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
@@ -2843,7 +2847,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total RWAs</t>
+          <t>Total Capital Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2892,6 +2896,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -2907,6 +2912,132 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="430" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3014,6 +3145,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -3022,131 +3154,6 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rathbones Investment Management Limited — Leverage Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Leverage Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="430" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
-FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
-Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
-SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
-LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3172,7 +3179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — LCR</t>
+          <t>Rathbones Investment Management Limited — Leverage Ratio</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3221,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>LCR</t>
+          <t>Leverage Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3263,6 +3270,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -3297,7 +3305,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — NSFR</t>
+          <t>Rathbones Investment Management Limited — LCR</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3347,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>NSFR</t>
+          <t>LCR</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3388,6 +3396,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -3422,7 +3431,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — MREL Ratio</t>
+          <t>Rathbones Investment Management Limited — NSFR</t>
         </is>
       </c>
     </row>
@@ -3464,7 +3473,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>MREL Ratio</t>
+          <t>NSFR</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3513,6 +3522,133 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="430" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -4200,6 +4336,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -4734,6 +4871,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -5170,6 +5308,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -5955,6 +6094,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -6275,6 +6415,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
 Note 14 (Loans and advances to customers) page references - FY2025/FY2024: p.39; FY2024/FY2023: p.41; FY2023/FY2022: p.41 (AR2023); FY2022/FY2021: p.43 (AR2022). FY2025's component lines sum to £206,393k against a reported net total of £206,392k - a genuine £1k source rounding artifact, not a transcription error; the reported net total is used for the Balance Sheet tie-out.</t>
@@ -6295,10 +6436,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -6309,17 +6450,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — CET1 Capital</t>
+          <t>Rathbones Investment Management Limited — KM1 Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Not applicable at this entity's level. Pillar 3 IS published and the UK KM1 template IS used - but only by the parent, Rathbones Group Plc, on a consolidated basis, which its own Pillar 3 states is the only basis of disclosure because no subsidiary is large enough to require individual disclosure (CRR Article 4(146)). Group KM1 figures are a different entity and a different basis from this entity-only workbook and are deliberately NOT reproduced. See the source note for the quoted evidence and the editions checked.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -6351,64 +6496,61 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>CET1 Capital</t>
+          <t>UK KM1 key-metrics template — Rathbones Investment Management Limited (entity)</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable — published only at Rathbones Group Plc consolidated level</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable — published only at Rathbones Group Plc consolidated level</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable — published only at Rathbones Group Plc consolidated level</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable — published only at Rathbones Group Plc consolidated level</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="430" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
-FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+          <t>Not applicable — published only at Rathbones Group Plc consolidated level</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="470" customHeight="1">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>Sources - the UK KM1 key-metrics template is NOT published for Rathbones Investment Management Limited in any year, and no figure on this sheet is withheld for want of looking. Positive evidence, from the publisher's own documents:
+• Rathbones Group Plc, Pillar 3 Disclosures 31 December 2025 (the NEWEST edition on rathbones.com as at 16 September 2026, found on the bank's own results/reports/presentations page rather than from a cited URL), section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf
+• The same document DOES print a 'UK KM1 - Key metrics template' (contents p.3; table at printed p.3, in GBP million), but its header block reads 'A summary of the Rathbones group's key ratios' and the table is Rathbones Group Plc CONSOLIDATED. That is a different reporting entity and a different basis from this workbook, whose every figure is Rathbones Investment Management Limited entity-only, so it is deliberately not reproduced here.
+• Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, same statement at section 1, printed p.6 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+• Rathbones Group Plc, Pillar 3 Semi-annual Disclosures 30 June 2025, section 1.2: 'We have no large subsidiaries meeting the...' [requirements for individual disclosure] - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf
+• The FY2025 annual edition also records (p.25 area, NSFR section) that Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly'. A RIM-solo regulatory position therefore EXISTS but goes to the regulator only; it is not published in any Pillar 3 template, and nothing has been derived from the Group figures to stand in for it.
+• THE PARENT'S PILLAR 3 WAS SEARCHED FOR A SUBSIDIARY BLOCK, which is the first place a UK subsidiary's regulatory figures normally live - not the last. It has none. The FY2025 edition was read end to end for an 'Individual'/'Solo'/'RIM' COLUMN inside a group table and for a separate subsidiary TABLE in an appendix (both of which exist at other UK groups), case-insensitively and with a richness control to prove the extraction was working ('capital' 96 hits, 'ratio' 135, 'cet1' 17, 'leverage' 20, 'RIM' 24). Findings, all negative for an entity-level figure: every KM1/OV1/CC1/CC2/LR/LIQ template in the document and in all ten appendices is captioned for the consolidated group; no template carries an entity column; and template UK CCA's row 6, 'Eligible at solo/(sub-)consolidated/solo&amp;(sub-)consolidated', reads 'Consolidated' for every one of the group's own-funds instruments. The 24 'RIM' mentions are all narrative - governance, committees, client lending, the liquidity buffer - and carry no RIM-solo regulatory figure. Appendix 1's excluded-templates listing likewise excludes templates on relevance and materiality grounds, not an entity-level annex.
+• The 30 June 2025 SEMI-ANNUAL edition was used as an independent second opinion at no transcription cost, and agrees: section 1.2 'We have no large subsidiaries meeting the...' requirements for individual disclosure, and its key-metrics table is likewise consolidated group only.
+• NOT BACK-FILLED FROM THE STATUTORY ACCOUNTS. The Company's own accounts do disclose a single entity-level own-funds total (see the Total Capital sheet), but that is a capital-management note, not a KM1 row, and it carries no tier split and no RWA. It is not mapped onto template row numbers here, because doing so would invent a correspondence the Company never published.
+• SOURCE DEFECT RECORDED, NOT CORRECTED (and not relied on, since nothing here is transcribed from it): the FY2025 annual edition's prose says its KM1 shows key ratios 'as at 31 December 2025', but the table's own column headers are printed 'c 30 June 2025' and 'e 31 December 2024'. Noted for a future reader who goes looking for 31 December 2025 columns in that document.
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6434,7 +6576,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — CET1 Ratio</t>
+          <t>Rathbones Investment Management Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -6476,7 +6618,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>CET1 Ratio</t>
+          <t>CET1 Capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -6525,6 +6667,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
@@ -6559,7 +6702,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Tier 1 Capital</t>
+          <t>Rathbones Investment Management Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6744,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 Capital</t>
+          <t>CET1 Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -6650,6 +6793,7 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>

--- a/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
+++ b/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
@@ -1517,6 +1517,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2473,34 +2474,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -2599,34 +2601,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -2852,34 +2855,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -2978,34 +2982,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3069,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Not publicly disclosed at entity level.</t>
+          <t>Not published at entity level - see the GA-020 evidence at the foot of the source note.</t>
         </is>
       </c>
     </row>
@@ -3108,27 +3113,27 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3152,9 @@
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
+Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -3226,34 +3233,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -3352,34 +3360,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -3478,34 +3487,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -3604,34 +3614,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -6623,34 +6634,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -6749,34 +6761,35 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>

--- a/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
+++ b/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
@@ -119,7 +119,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2413,7 +2413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
@@ -2506,7 +2506,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="430" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2518,7 +2518,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -2526,9 +2533,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2540,7 +2548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2625,7 +2633,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
@@ -2633,7 +2641,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="430" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2645,7 +2653,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -2653,9 +2668,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2667,7 +2683,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -2746,14 +2762,14 @@
         <v>237897</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="52" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: ENTITY-LEVEL own-funds total taken from the Company's own statutory accounts, not from a Pillar 3 template - Rathbones Group Plc's Pillar 3 is consolidated only and discloses nothing at this entity's level. No tier split or RWA accompanies it, so no ratio on this sheet or the Total Capital Ratio / Total RWAs sheets is derivable from it. The FY2024-to-FY2025 near-doubling is genuine and reflects the migration of Investec Wealth &amp; Investment clients into this entity, which also drives the Balance Sheet and equity jump visible on the Overview sheet.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="470" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2765,7 +2781,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
@@ -2780,9 +2803,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2794,7 +2818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2879,7 +2903,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
@@ -2887,7 +2911,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="430" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -2899,7 +2923,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -2907,9 +2938,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2921,7 +2953,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3006,7 +3038,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
@@ -3014,7 +3046,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="430" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3026,7 +3058,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -3034,9 +3073,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3048,7 +3088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -3137,7 +3177,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="430" customHeight="1">
+    <row r="6" ht="409" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3149,7 +3189,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="409" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
@@ -3159,7 +3206,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3172,7 +3220,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3257,15 +3305,17 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="221" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
-GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="430" customHeight="1">
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.
+GA-026 (2026-10-09) - CHECKED AGAINST THE GROUP'S OWN LEVERAGE TEMPLATE, AND STILL NOT AN ADD. This sweep looked for banks publishing BOTH UK leverage bases (template UK LR2 prints the including-claims-on-central-banks measure at row 24 / UK-25c and the excluding one at UK-24b / row 25). Rathbones DOES publish a full UK LR2 with both: the 31 December 2023 Pillar 3 disclosures, p.45, 'Template UK LR2 - LRCom', gives row 23 431.4; row 24 3,345.8; UK-24a (1,038.8); UK-24b 2,307.0; row 25 18.70%; UK-25c 12.89% at 31 December 2023, with 298.7 / 3,104.6 / (1,410.1) / 1,694.3 / 17.63% / 9.62% at 31 December 2022.
+NONE OF IT BELONGS ON THIS SHEET, because that template is RATHBONES GROUP PLC CONSOLIDATED and this workbook is the entity. It is the same reason the sheet says 'not publicly disclosed' in the first place, and the same trap that stopped two other banks in this batch whose LR2 turned out to be group-level. The figures are recorded here so a later pass does not have to re-find them and does not mistake their existence for a gap on this sheet. Nothing is carried across consolidation levels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3277,7 +3327,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -3285,9 +3342,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3299,7 +3357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3384,7 +3442,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
@@ -3392,7 +3450,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="430" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3404,7 +3462,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -3412,9 +3477,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3426,7 +3492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3511,7 +3577,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
@@ -3519,7 +3585,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="430" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3531,7 +3597,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -3539,9 +3612,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3553,7 +3627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3638,7 +3712,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
@@ -3646,7 +3720,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="430" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -3658,7 +3732,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -3666,9 +3747,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3680,7 +3762,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -4335,7 +4417,7 @@
         <v>2843239</v>
       </c>
     </row>
-    <row r="35" ht="280" customHeight="1">
+    <row r="35" ht="377" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory accounts, entity basis, GBP'000.
@@ -4347,15 +4429,23 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
-LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="280" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A37:F37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4367,7 +4457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="76" customWidth="1" min="1" max="1"/>
@@ -4870,7 +4960,7 @@
         <v>58964</v>
       </c>
     </row>
-    <row r="27" ht="280" customHeight="1">
+    <row r="27" ht="377" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory accounts, entity basis, GBP'000.
@@ -4882,14 +4972,22 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
-LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="280" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A29:F29"/>
     <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4902,7 +5000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -5307,7 +5405,7 @@
         <v>1147348</v>
       </c>
     </row>
-    <row r="25" ht="260" customHeight="1">
+    <row r="25" ht="351" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory accounts, entity basis, GBP'000.
@@ -5318,7 +5416,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="260" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -5326,8 +5431,9 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A27:F27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5339,7 +5445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="86" customWidth="1" min="1" max="1"/>
@@ -6092,7 +6198,7 @@
         <v>1530445</v>
       </c>
     </row>
-    <row r="40" ht="470" customHeight="1">
+    <row r="40" ht="409" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -6105,15 +6211,23 @@
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
-LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="409" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A42:F42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6125,7 +6239,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -6414,7 +6528,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="280" customHeight="1">
+    <row r="16" ht="390" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory accounts, entity basis, GBP'000.
@@ -6427,15 +6541,23 @@
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
-LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="280" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
 Note 14 (Loans and advances to customers) page references - FY2025/FY2024: p.39; FY2024/FY2023: p.41; FY2023/FY2022: p.41 (AR2023); FY2022/FY2021: p.43 (AR2022). FY2025's component lines sum to £206,393k against a reported net total of £206,392k - a genuine £1k source rounding artifact, not a transcription error; the reported net total is used for the Balance Sheet tie-out.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A18:F18"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6447,7 +6569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -6536,7 +6658,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="470" customHeight="1">
+    <row r="6" ht="409" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Sources - the UK KM1 key-metrics template is NOT published for Rathbones Investment Management Limited in any year, and no figure on this sheet is withheld for want of looking. Positive evidence, from the publisher's own documents:
@@ -6548,7 +6670,14 @@
 • THE PARENT'S PILLAR 3 WAS SEARCHED FOR A SUBSIDIARY BLOCK, which is the first place a UK subsidiary's regulatory figures normally live - not the last. It has none. The FY2025 edition was read end to end for an 'Individual'/'Solo'/'RIM' COLUMN inside a group table and for a separate subsidiary TABLE in an appendix (both of which exist at other UK groups), case-insensitively and with a richness control to prove the extraction was working ('capital' 96 hits, 'ratio' 135, 'cet1' 17, 'leverage' 20, 'RIM' 24). Findings, all negative for an entity-level figure: every KM1/OV1/CC1/CC2/LR/LIQ template in the document and in all ten appendices is captioned for the consolidated group; no template carries an entity column; and template UK CCA's row 6, 'Eligible at solo/(sub-)consolidated/solo&amp;(sub-)consolidated', reads 'Consolidated' for every one of the group's own-funds instruments. The 24 'RIM' mentions are all narrative - governance, committees, client lending, the liquidity buffer - and carry no RIM-solo regulatory figure. Appendix 1's excluded-templates listing likewise excludes templates on relevance and materiality grounds, not an entity-level annex.
 • The 30 June 2025 SEMI-ANNUAL edition was used as an independent second opinion at no transcription cost, and agrees: section 1.2 'We have no large subsidiaries meeting the...' requirements for individual disclosure, and its key-metrics table is likewise consolidated group only.
 • NOT BACK-FILLED FROM THE STATUTORY ACCOUNTS. The Company's own accounts do disclose a single entity-level own-funds total (see the Total Capital sheet), but that is a capital-management note, not a KM1 row, and it carries no tier split and no RWA. It is not mapped onto template row numbers here, because doing so would invent a correspondence the Company never published.
-• SOURCE DEFECT RECORDED, NOT CORRECTED (and not relied on, since nothing here is transcribed from it): the FY2025 annual edition's prose says its KM1 shows key ratios 'as at 31 December 2025', but the table's own column headers are printed 'c 30 June 2025' and 'e 31 December 2024'. Noted for a future reader who goes looking for 31 December 2025 columns in that document.
+• SOURCE DEFECT RECORDED, NOT CORRECTED (and not relied on, since nothing here is transcribed from it): the FY2025 annual edition's prose says its KM1 shows key ratios 'as at 31 December 2025', but the table's own column headers are printed 'c 30 June 2025' and 'e 31 December 2024'. Noted for a future reader who goes looking for 31 December 2025 columns in that document.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="409" customHeight="1">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
@@ -6560,7 +6689,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6573,7 +6703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6658,7 +6788,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
@@ -6666,7 +6796,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="430" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -6678,7 +6808,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -6686,9 +6823,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6700,7 +6838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -6785,7 +6923,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
@@ -6793,7 +6931,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="430" customHeight="1">
+    <row r="7" ht="409" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
@@ -6805,7 +6943,14 @@
 Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
 Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
 SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
 The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
@@ -6813,9 +6958,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
+++ b/banks/RATHBONES INVESTMENT MANAGEMENT FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2427,7 +2428,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Tier 1 Capital</t>
+          <t>Rathbones Investment Management Limited — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2470,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 Capital</t>
+          <t>CET1 Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2562,7 +2563,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Tier 1 Ratio</t>
+          <t>Rathbones Investment Management Limited — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2605,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 Ratio</t>
+          <t>Tier 1 Capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -2686,7 +2687,7 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2697,16 +2698,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Total Capital</t>
+          <t>Rathbones Investment Management Limited — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>£'000</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2743,29 +2740,40 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Regulatory capital resources (own funds) — Company entity level</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>467062</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>261190</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>267182</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>256378</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>237897</v>
-      </c>
-    </row>
-    <row r="5" ht="52" customHeight="1">
+          <t>Tier 1 Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="117" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: ENTITY-LEVEL own-funds total taken from the Company's own statutory accounts, not from a Pillar 3 template - Rathbones Group Plc's Pillar 3 is consolidated only and discloses nothing at this entity's level. No tier split or RWA accompanies it, so no ratio on this sheet or the Total Capital Ratio / Total RWAs sheets is derivable from it. The FY2024-to-FY2025 near-doubling is genuine and reflects the migration of Investec Wealth &amp; Investment clients into this entity, which also drives the Balance Sheet and equity jump visible on the Overview sheet.</t>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
         </is>
       </c>
     </row>
@@ -2791,14 +2799,7 @@
           <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
-ENTITY-LEVEL REGULATORY CAPITAL RESOURCES (added 2026-09-15). Each year's own Annual Report and Financial Statements, capital-management note (scanned filings - figures read by OCR at 300-400 dpi and confirmed visually):
-FY2025 and FY2024 comparative: 'At 31 December 2025, the Company's regulatory capital resources, including retained earnings for 2025, were GBP467,062,000 (2024: GBP261,190,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 own-year, and FY2023 comparative: 'At 31 December 2024 ... were GBP261,190,000 (2023: GBP267,182,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 own-year, and FY2022 comparative: 'At 31 December 2023 ... were GBP267,182,000 (2022: GBP256,378,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021 own-year: 'At 31 December 2021 ... were GBP237,897,000 (2020: GBP247,786,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
-VALIDATION: every year except FY2022 and FY2025 appears in two separate filings and agrees in both - FY2024 reads GBP261,190,000 in both the FY2025 comparative and the FY2024 own-year note, and FY2023 reads GBP267,182,000 in both the FY2024 comparative and the FY2023 own-year note.
-BASIS: this is the Company's total regulatory capital RESOURCES (own funds) as defined in its own note - 'accounting capital and certain deductions from accounting capital, the latter largely in respect of intangible assets', measured against Pillar I and Pillar II requirements under the PRA's application of CRD. The note gives NO tier split and NO risk-weighted assets, so CET1 Capital, Tier 1 Capital, all three capital ratios and Total RWAs remain blank rather than derived - in particular this figure has NOT been copied into CET1 or Tier 1, because the Company nowhere states that its capital is wholly CET1.</t>
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2822,7 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2832,12 +2833,16 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Total Capital Ratio</t>
+          <t>Rathbones Investment Management Limited — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>£'000</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2874,40 +2879,29 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total Capital Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="117" customHeight="1">
+          <t>Regulatory capital resources (own funds) — Company entity level</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>467062</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>261190</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>267182</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>256378</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>237897</v>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
-GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
+          <t>Note: ENTITY-LEVEL own-funds total taken from the Company's own statutory accounts, not from a Pillar 3 template - Rathbones Group Plc's Pillar 3 is consolidated only and discloses nothing at this entity's level. No tier split or RWA accompanies it, so no ratio on this sheet or the Total Capital Ratio / Total RWAs sheets is derivable from it. The FY2024-to-FY2025 near-doubling is genuine and reflects the migration of Investec Wealth &amp; Investment clients into this entity, which also drives the Balance Sheet and equity jump visible on the Overview sheet.</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2927,14 @@
           <t>(continued)
 LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
 LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.
+ENTITY-LEVEL REGULATORY CAPITAL RESOURCES (added 2026-09-15). Each year's own Annual Report and Financial Statements, capital-management note (scanned filings - figures read by OCR at 300-400 dpi and confirmed visually):
+FY2025 and FY2024 comparative: 'At 31 December 2025, the Company's regulatory capital resources, including retained earnings for 2025, were GBP467,062,000 (2024: GBP261,190,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 own-year, and FY2023 comparative: 'At 31 December 2024 ... were GBP261,190,000 (2023: GBP267,182,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 own-year, and FY2022 comparative: 'At 31 December 2023 ... were GBP267,182,000 (2022: GBP256,378,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021 own-year: 'At 31 December 2021 ... were GBP237,897,000 (2020: GBP247,786,000).' - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+VALIDATION: every year except FY2022 and FY2025 appears in two separate filings and agrees in both - FY2024 reads GBP261,190,000 in both the FY2025 comparative and the FY2024 own-year note, and FY2023 reads GBP267,182,000 in both the FY2024 comparative and the FY2023 own-year note.
+BASIS: this is the Company's total regulatory capital RESOURCES (own funds) as defined in its own note - 'accounting capital and certain deductions from accounting capital, the latter largely in respect of intangible assets', measured against Pillar I and Pillar II requirements under the PRA's application of CRD. The note gives NO tier split and NO risk-weighted assets, so CET1 Capital, Tier 1 Capital, all three capital ratios and Total RWAs remain blank rather than derived - in particular this figure has NOT been copied into CET1 or Tier 1, because the Company nowhere states that its capital is wholly CET1.</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2968,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — Total RWAs</t>
+          <t>Rathbones Investment Management Limited — Total Capital Ratio</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3010,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total RWAs</t>
+          <t>Total Capital Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3083,6 +3084,141 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="117" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="409" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3209,143 +3345,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rathbones Investment Management Limited — Leverage Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Leverage Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="221" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
-GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.
-GA-026 (2026-10-09) - CHECKED AGAINST THE GROUP'S OWN LEVERAGE TEMPLATE, AND STILL NOT AN ADD. This sweep looked for banks publishing BOTH UK leverage bases (template UK LR2 prints the including-claims-on-central-banks measure at row 24 / UK-25c and the excluding one at UK-24b / row 25). Rathbones DOES publish a full UK LR2 with both: the 31 December 2023 Pillar 3 disclosures, p.45, 'Template UK LR2 - LRCom', gives row 23 431.4; row 24 3,345.8; UK-24a (1,038.8); UK-24b 2,307.0; row 25 18.70%; UK-25c 12.89% at 31 December 2023, with 298.7 / 3,104.6 / (1,410.1) / 1,694.3 / 17.63% / 9.62% at 31 December 2022.
-NONE OF IT BELONGS ON THIS SHEET, because that template is RATHBONES GROUP PLC CONSOLIDATED and this workbook is the entity. It is the same reason the sheet says 'not publicly disclosed' in the first place, and the same trap that stopped two other banks in this batch whose LR2 turned out to be group-level. The figures are recorded here so a later pass does not have to re-find them and does not mistake their existence for a gap on this sheet. Nothing is carried across consolidation levels.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="409" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
-FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
-Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
-SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="409" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>(continued)
-LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
-LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3371,7 +3370,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — LCR</t>
+          <t>Rathbones Investment Management Limited — Leverage Ratio</t>
         </is>
       </c>
     </row>
@@ -3413,7 +3412,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>LCR</t>
+          <t>Leverage Ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3442,11 +3441,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="117" customHeight="1">
+    <row r="5" ht="221" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
           <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
-GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.
+GA-026 (2026-10-09) - CHECKED AGAINST THE GROUP'S OWN LEVERAGE TEMPLATE, AND STILL NOT AN ADD. This sweep looked for banks publishing BOTH UK leverage bases (template UK LR2 prints the including-claims-on-central-banks measure at row 24 / UK-25c and the excluding one at UK-24b / row 25). Rathbones DOES publish a full UK LR2 with both: the 31 December 2023 Pillar 3 disclosures, p.45, 'Template UK LR2 - LRCom', gives row 23 431.4; row 24 3,345.8; UK-24a (1,038.8); UK-24b 2,307.0; row 25 18.70%; UK-25c 12.89% at 31 December 2023, with 298.7 / 3,104.6 / (1,410.1) / 1,694.3 / 17.63% / 9.62% at 31 December 2022.
+NONE OF IT BELONGS ON THIS SHEET, because that template is RATHBONES GROUP PLC CONSOLIDATED and this workbook is the entity. It is the same reason the sheet says 'not publicly disclosed' in the first place, and the same trap that stopped two other banks in this batch whose LR2 turned out to be group-level. The figures are recorded here so a later pass does not have to re-find them and does not mistake their existence for a gap on this sheet. Nothing is carried across consolidation levels.</t>
         </is>
       </c>
     </row>
@@ -3506,7 +3507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — NSFR</t>
+          <t>Rathbones Investment Management Limited — LCR</t>
         </is>
       </c>
     </row>
@@ -3548,7 +3549,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>NSFR</t>
+          <t>LCR</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -3641,7 +3642,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — MREL Ratio</t>
+          <t>Rathbones Investment Management Limited — NSFR</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3684,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>MREL Ratio</t>
+          <t>NSFR</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -4451,6 +4452,141 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="117" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
+GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="409" customHeight="1">
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
+FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
+FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
+FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
+Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
+Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
+SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="409" customHeight="1">
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>(continued)
+LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
+LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
+The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6569,6 +6705,257 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rathbones Investment Management Limited — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>10.45%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>3.99%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>12.01%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>9.92%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>7.07%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>4.04%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>12.01%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>9.85%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>14.38%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.56%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>1.38%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>1.69%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.54%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>1.76%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>2.07%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Average net operating basis point return (as published)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>79.7bps</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Basis point return on funds under management and administration (as published)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>70.4bps</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="260" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Note: TWO KINDS OF FIGURE, NEVER MERGED. The rows above are not one series. The 'Return on equity/assets' rows are THIS PROJECT'S OWN ARITHMETIC on the figures printed on this workbook's statement sheets. The rows marked '(as published)' are the bank's own published ratios, quoted verbatim, each struck on the bank's own definition - which differs from bank to bank and usually from ours, most often in whether the numerator is before or after tax and whether the denominator is average, opening or year-end equity, tangible equity or required equity. They are not averaged, reconciled, or substituted for one another, and where they disagree both stand: the disagreement is the finding.
+THE BANK'S OWN DEFINITIONS, VERBATIM. Average net operating basis point return: “Income margins are expressed as a basis point return (‘bps’), which depends on a mix of tiered annual fee rates, commissions charged for transactions undertaken on behalf of clients and the interest margin earned on the cash element of client portfolios (which represent banking deposits within the Company) and on loans extended to clients.” Basis point return on funds under management and administration: “Fee or commission income (see table 3), divided by the average funds under management and administration on the quarterly billing dates (see table 4)”
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return. The two diverge most in FY2025, where return on equity is 10.45% on an average basis and 7.07% on a year-end basis.
+FY2021 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2021 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2021 because it needs only the closing balance.
+FIGURES THE BANK PUBLISHED ONLY AS A LATER EDITION'S COMPARATIVE, AND WHY THEY ARE NOT IN THE CELLS ABOVE. FY2024 Average net operating basis point return 75.7bps; FY2024 Basis point return on funds under management and administration 65.2bps. Each year's cell carries what that year's OWN annual report printed. A comparative restated in a later edition is a different claim - it may rest on a revised definition, a restated perimeter or a corrected prior figure - so it is recorded here rather than substituted into the year it refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="170" customHeight="1">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit for the year attributable to equity holders of the company” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Rathbones Investment Management Limited's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The '(as published)' rows are quoted verbatim from Rathbones Investment Management Limited's own disclosures and are recorded, with the exact document, page and verification state for each, in research/profitability/published_returns.jsonl under ‘RATHBONES INVESTMENT MANAGEMENT’.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6692,141 +7079,6 @@
   <mergeCells count="2">
     <mergeCell ref="A8:F8"/>
     <mergeCell ref="A6:F6"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rathbones Investment Management Limited — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>CET1 Capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no RIM entity figure: Rathbones Group Plc Pillar 3 FY2021–FY2025, s.1 Executive summary, says disclosure is group-consolidated only (no large subsidiary, CRR 4(146)); RIM's own accounts print none.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="117" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Note: Not publicly disclosed at Rathbones Investment Management Limited entity level. Rathbones Group Plc's official Pillar 3 reports are consolidated and state that no large subsidiary meets the definition requiring individual disclosure; group metrics must not be substituted for this Company's metrics. See the source note.
-GA-020 EVIDENCE, ALL FIVE YEARS (2026-09-19): the same statement 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146)' appears in Rathbones Group Plc Pillar 3 FY2021 (PDF p.5) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/pillar_3_dec_2021_final.pdf ; FY2022 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/rathbones_pillar_3_december_2022_final3.pdf ; FY2023 (PDF p.7) - https://www.rathbones.com/sites/main/files/wealth-management/results_and_presentations/files/31_december_2023_pillar_3_disclosures_final.pdf ; and the FY2024 and FY2025 editions (printed p.6) cited in the source note. No edition prints a RIM-solo figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="409" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Sources - Rathbones Investment Management Limited statutory Statement of cash flows, GBP'000. Each year's own column was checked against the next year's comparative column where available.
-FY2025 and FY2024 comparative: Annual report and financial statements 2025, p.25 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzUyMjY1MjQyNWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2024 and FY2023 comparative: Annual report and financial statements 2024, p.28 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQ3MzI5ODI4OWFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2023 and FY2022 comparative: Annual report and financial statements 2023, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzQyMjI5MjUwM2FkaXF6a2N4/document?download=0&amp;format=pdf
-FY2022 and FY2021 comparative: Annual report and financial statements 2022, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM4MTE3NjI0OGFkaXF6a2N4/document?download=0&amp;format=pdf
-FY2021: Annual report and financial statements 2021, p.29 - https://find-and-update.company-information.service.gov.uk/company/01448919/filing-history/MzM0MjM1MjU5OWFkaXF6a2N4/document?download=0&amp;format=pdf
-Entity: Rathbones Investment Management Limited (FRN 116316, company 01448919), formerly Rathbone Investment Management Limited until 7 December 2022. The Company is a wholly-owned subsidiary of Rathbones Group Plc and prepares entity-only IFRS financial statements under the Companies Act 2006 Section 400 exemption from consolidated accounts. Figures are GBP'000. The Company is an investment and wealth-management business, not the consolidated Rathbones Group.
-Pillar 3 metrics are not substituted from Rathbones Group Plc: the official 2024 Pillar 3 report states that disclosures are consolidated and that no large subsidiary meets the definition requiring individual disclosure. Accordingly, entity-level CET1, Tier 1, Total Capital, RWA, leverage, LCR, NSFR and MREL figures are not publicly disclosed in the Company's accounts.
-SOURCE FOR THAT STATEMENT (citation added 15 September 2026 - the document was named here but its URL was previously not printed on any sheet): Rathbones Group Plc, Pillar 3 Disclosures 31 December 2024, section 1 'Executive summary', p.6 - 'Disclosures are made on a consolidated group level, as we have no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-BASIS WARNING - this Group document is cited ONLY as evidence of ABSENCE, i.e. as the reason the entity-level Pillar 3 sheets in this workbook are blank. Not one figure in this workbook is taken from it. Every figure here comes from Rathbones Investment Management Limited's own entity-only statutory accounts filed at Companies House under company number 01448919. Re-checked 15 September 2026 against the replacement document in full: it discloses no RIM-solo quantitative metric anywhere. Its NSFR section (p.25) does say Rathbones 'is required to calculate and monitor the ratio on a RIM-solo and group consolidated basis, reporting the positions quarterly', but it prints only the group consolidated figures - templates UK KM1, UK LIQ1 and UK LIQ2 are all group-level - so there is no solo-consolidation or significant-subsidiary annex to draw entity data from, and no Group figure has been substituted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="409" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>(continued)
-LATEST-EDITION CHECK (16 September 2026): rathbones.com's own investor page was checked directly and now carries a NEWER annual edition, Rathbones Group Plc Pillar 3 Disclosures 31 December 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/31_december_2025_pillar_3_discosures.pdf - plus a semi-annual edition at 30 June 2025 - https://www.rathbones.com/sites/main/files/results_and_presentations/files/interim_pillar_3_disclosures_30_june_2025_1.pdf. The FY2025 edition repeats the consolidated-only position verbatim at section 1 'Executive summary', printed p.6: 'Disclosures are made on a consolidated group level, as the grouphave [sic] no large subsidiaries meeting the requirements for individual disclosure under the definition within CRR Article 4(146).' Its only KM1 is again a Rathbones Group Plc consolidated table, so nothing in this entity-level workbook changes; no figure has been taken from it either.
-LINK PROVENANCE (15 September 2026): the URL above is a REPLACEMENT. rathbones.com renamed its site directory from /sites/rathbones.com/ to /sites/main/, so the URL originally cited for this document now returns HTTP 404. Dead original, kept so the provenance chain stays readable: https://www.rathbones.com/sites/rathbones.com/files/results_and_presentations/files/31_december_2024_pillar_3_disclosures.pdf
-The 2021 own-account closing cash (£1,530,445k) does not equal the 2022 account's comparative opening cash (£1,527,887k); both source-presented figures are retained and the difference is not inferred or forced.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6852,7 +7104,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rathbones Investment Management Limited — CET1 Ratio</t>
+          <t>Rathbones Investment Management Limited — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -6894,7 +7146,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>CET1 Ratio</t>
+          <t>CET1 Capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
